--- a/backtest_runs/20260410_193731/by_symbol/DOL/DOL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/DOL/DOL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>-17534.52000000001</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>89670.44</v>
@@ -771,7 +771,7 @@
         <v>-2389.399999999995</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>91361.40000000001</v>
@@ -817,7 +817,7 @@
         <v>-1249.839999999999</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>90111.56000000001</v>
@@ -863,7 +863,7 @@
         <v>-2168.84</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>87942.72</v>
@@ -955,7 +955,7 @@
         <v>-257.3200000000011</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>87979.48</v>
@@ -1047,7 +1047,7 @@
         <v>-624.9200000000062</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>87648.64</v>
@@ -1185,7 +1185,7 @@
         <v>-1249.840000000012</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>89964.51999999999</v>
@@ -1231,7 +1231,7 @@
         <v>-257.319999999988</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>89707.20000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-2830.520000000011</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>86876.67999999999</v>
@@ -1323,7 +1323,7 @@
         <v>-771.95999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>86104.72</v>
@@ -1415,7 +1415,7 @@
         <v>-1029.280000000004</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>87428.08</v>
@@ -1461,7 +1461,7 @@
         <v>-808.7199999999958</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>86619.36000000002</v>
